--- a/minidetective_roi.xlsx
+++ b/minidetective_roi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsy0714\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsy0714\minidetective\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF40C3AB-164B-41A5-B850-3134495AF8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1CA4B9-F3D0-42F9-A175-FEB3AE0D5F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45300" yWindow="3555" windowWidth="28800" windowHeight="15345" xr2:uid="{BA0EDA45-A830-4C17-9D23-77209FD80E08}"/>
+    <workbookView xWindow="42870" yWindow="4635" windowWidth="28800" windowHeight="15345" xr2:uid="{BA0EDA45-A830-4C17-9D23-77209FD80E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -161,35 +161,11 @@
     <xf numFmtId="38" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -200,21 +176,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -566,7 +528,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D1" s="8"/>
+      <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
     </row>
@@ -650,23 +612,27 @@
       <c r="B5" s="2">
         <v>46107</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3">
+        <v>136432</v>
+      </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5:D68" si="3">C5-C4</f>
-        <v>-135233</v>
-      </c>
-      <c r="E5" s="3"/>
+        <v>1199</v>
+      </c>
+      <c r="E5" s="3">
+        <v>14461</v>
+      </c>
       <c r="F5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12291.85</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" si="1"/>
-        <v>135233</v>
+        <v>11092.85</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>9.2517514595496255</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
@@ -676,7 +642,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-136432</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6">
@@ -685,11 +651,11 @@
       </c>
       <c r="G6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>136432</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="2"/>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
@@ -4743,11 +4709,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H3:H182">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>H3&gt;=20%</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>H3&lt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>H3&gt;=20%</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
